--- a/src/test/resources/data/endpoints.xlsx
+++ b/src/test/resources/data/endpoints.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="119">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -103,7 +103,7 @@
     <t>POST_MissingEmailDomain.json</t>
   </si>
   <si>
-    <t>Expected- 400 bad request. Actual- 201 created</t>
+    <t>Email should be in correct format</t>
   </si>
   <si>
     <t>MinimalValidFields</t>
@@ -166,44 +166,215 @@
     <t>ExistingUserFirstname</t>
   </si>
   <si>
+    <t>/uap/users/username/</t>
+  </si>
+  <si>
+    <t>NonExistUserFirstname</t>
+  </si>
+  <si>
+    <t>/uap/users/username/Angitha</t>
+  </si>
+  <si>
+    <t>ExistingUserLastname</t>
+  </si>
+  <si>
+    <t>/uap/users/username/Ninja</t>
+  </si>
+  <si>
+    <t>SpecialCharFirstname</t>
+  </si>
+  <si>
+    <t>/uap/users/username/#Manu</t>
+  </si>
+  <si>
+    <t>SpaceExistFirstname</t>
+  </si>
+  <si>
+    <t>/uap/users/username/  Numpy</t>
+  </si>
+  <si>
+    <t>Numeric</t>
+  </si>
+  <si>
+    <t>/uap/users/username/1234</t>
+  </si>
+  <si>
+    <t>NoEndpoint</t>
+  </si>
+  <si>
+    <t>UpdateValidInputs</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>/uap/updateuser/</t>
+  </si>
+  <si>
+    <t>PUT_ValidUpdate.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidUserId</t>
+  </si>
+  <si>
+    <t>/uap/updateuser/21abc</t>
+  </si>
+  <si>
+    <t>PUT_InvalidUserId.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidContact</t>
+  </si>
+  <si>
+    <t>/uap/updateuser/21950</t>
+  </si>
+  <si>
+    <t>PUT_InvalidContact.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidEmailId</t>
+  </si>
+  <si>
+    <t>PUT_InvalidEmail.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidFirstName</t>
+  </si>
+  <si>
+    <t>PUT_InvalidFirstName.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidLastName</t>
+  </si>
+  <si>
+    <t>PUT_InvalidLastName.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidplotNumber</t>
+  </si>
+  <si>
+    <t>PUT_InvalidPlot.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidStreet</t>
+  </si>
+  <si>
+    <t>PUT_InvalidStreet.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidState</t>
+  </si>
+  <si>
+    <t>PUT_InvalidState.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidCountry</t>
+  </si>
+  <si>
+    <t>PUT_InvalidCountry.json</t>
+  </si>
+  <si>
+    <t>UpdateWithInvalidZipcode</t>
+  </si>
+  <si>
+    <t>PUT_InvalidZipcode.json</t>
+  </si>
+  <si>
+    <t>ExistingUserId</t>
+  </si>
+  <si>
     <t>DELETE</t>
   </si>
   <si>
+    <t>/uap/deleteuser/</t>
+  </si>
+  <si>
+    <t>DeleteNonExistUserId</t>
+  </si>
+  <si>
+    <t>/uap/deleteuser/44561</t>
+  </si>
+  <si>
+    <t>EmptyUserId</t>
+  </si>
+  <si>
+    <t>SpecialCharUserId</t>
+  </si>
+  <si>
+    <t>/uap/deleteuser/*@1234</t>
+  </si>
+  <si>
+    <t>SpaceExistUserId</t>
+  </si>
+  <si>
+    <t>/uap/deleteuser/      34343</t>
+  </si>
+  <si>
+    <t>DeleteExistingUserFirstname</t>
+  </si>
+  <si>
     <t>/uap/deleteuser/username/</t>
   </si>
   <si>
-    <t>NonExistUserFirstname</t>
-  </si>
-  <si>
-    <t>EmptyUserFirstname</t>
-  </si>
-  <si>
-    <t>SpecialCharFirstname</t>
-  </si>
-  <si>
-    <t>/uap/deleteuser/username/*Anu</t>
-  </si>
-  <si>
-    <t>MultipleUsers</t>
-  </si>
-  <si>
-    <t>/uap/deleteuser/username/hhsh</t>
-  </si>
-  <si>
-    <t>Expected: 200, but got: 404 expected [200] but found [404]</t>
-  </si>
-  <si>
-    <t>SpaceExistFirstname</t>
-  </si>
-  <si>
-    <t>/uap/deleteuser/username/   Manu</t>
+    <t>DeleteNonExistUserFirstname</t>
+  </si>
+  <si>
+    <t>/uap/deleteuser/username/Angitha</t>
+  </si>
+  <si>
+    <t>DeleteEmptyUserFirstname</t>
+  </si>
+  <si>
+    <t>DeleteSpecialCharFirstname</t>
+  </si>
+  <si>
+    <t>/uap/deleteuser/username/*@Ankitha</t>
+  </si>
+  <si>
+    <t>DeleteSpaceExistFirstname</t>
+  </si>
+  <si>
+    <t>/uap/deleteuser/username/     Manu</t>
+  </si>
+  <si>
+    <t>UpdateOnlyFirstName</t>
+  </si>
+  <si>
+    <t>PATCH</t>
+  </si>
+  <si>
+    <t>/uap/updateuserfields/</t>
+  </si>
+  <si>
+    <t>PATCH_FirstName.json</t>
+  </si>
+  <si>
+    <t>UpdateOnlyNoFirstName</t>
+  </si>
+  <si>
+    <t>PATCH_InvalidFirstName.json</t>
+  </si>
+  <si>
+    <t>UPdateOnlyInvalidContact</t>
+  </si>
+  <si>
+    <t>PATCH_InvalidContact.json</t>
+  </si>
+  <si>
+    <t>UPdateOnlyInvalidEmail</t>
+  </si>
+  <si>
+    <t>PATCH_InvalidEmail.json</t>
+  </si>
+  <si>
+    <t>PATCH_UpdateEmailWithNumber.json</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -224,23 +395,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <color rgb="FFEBEBEB"/>
-      <name val="Consolas"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F2F2F"/>
-        <bgColor rgb="FF2F2F2F"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -249,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -275,9 +436,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,14 +650,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.25"/>
+    <col customWidth="1" min="1" max="1" width="47.88"/>
     <col customWidth="1" min="2" max="2" width="12.5"/>
     <col customWidth="1" min="3" max="3" width="16.25"/>
-    <col customWidth="1" min="4" max="4" width="18.75"/>
-    <col customWidth="1" min="5" max="5" width="28.88"/>
+    <col customWidth="1" min="4" max="4" width="18.5"/>
+    <col customWidth="1" min="5" max="5" width="32.0"/>
     <col customWidth="1" min="6" max="6" width="16.25"/>
-    <col customWidth="1" min="7" max="7" width="36.5"/>
-    <col customWidth="1" min="8" max="8" width="56.13"/>
+    <col customWidth="1" min="7" max="7" width="28.88"/>
+    <col customWidth="1" min="8" max="8" width="36.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -694,20 +852,17 @@
       <c r="E10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="9">
         <v>400.0</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="J10" s="8">
-        <v>400.0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -905,34 +1060,39 @@
         <v>50</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="F21" s="3">
         <v>200.0</v>
       </c>
-      <c r="H21" s="2"/>
+      <c r="I21" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="F22" s="3">
         <v>404.0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -940,53 +1100,59 @@
         <v>54</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F23" s="3">
-        <v>400.0</v>
+        <v>404.0</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24" s="3">
         <v>404.0</v>
       </c>
+      <c r="I24" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F25" s="3">
-        <v>200.0</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>59</v>
+        <v>404.0</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -994,7 +1160,7 @@
         <v>60</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="D26" s="3" t="b">
         <v>0</v>
@@ -1005,38 +1171,589 @@
       <c r="F26" s="3">
         <v>404.0</v>
       </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1"/>
+      <c r="I26" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="3">
+        <v>404.0</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="3">
+        <v>404.0</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" s="3">
+        <v>404.0</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F45" s="3">
+        <v>404.0</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="3">
+        <v>404.0</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F49" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F50" s="3">
+        <v>404.0</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" s="3">
+        <v>404.0</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F53" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F54" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F55" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F56" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
     <row r="58" ht="15.75" customHeight="1"/>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -1983,6 +2700,18 @@
     <row r="1001" ht="15.75" customHeight="1"/>
     <row r="1002" ht="15.75" customHeight="1"/>
     <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
